--- a/基本設計/22_バッチ非機能運用_基本設計書.xlsx
+++ b/基本設計/22_バッチ非機能運用_基本設計書.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R0cb7615ed7274021"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R047221ebec774e82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="37_バッチ" sheetId="38" r:id="Reb2b497fc3c0452c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="38_性能・可用性" sheetId="39" r:id="R96f013af65154dd3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="39_バックアップ" sheetId="40" r:id="R2f2655c0429d4fea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="40_環境・監査・配備" sheetId="41" r:id="Re62b1750b3cd4135"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R8d97997e20c64753"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R0efe5b648ac3474c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="37_バッチ" sheetId="38" r:id="R8a31019fed8c4daa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="38_性能・可用性" sheetId="39" r:id="Re294ad7f503f4487"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="39_バックアップ" sheetId="40" r:id="R80a37383c1e44f8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="40_環境・監査・配備" sheetId="41" r:id="R1e84c7e592f24da8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1108,10 +1108,7 @@
       <x:c r="F16" s="140"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.8 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
+      <x:c r="A17"/>
       <x:c r="C17"/>
       <x:c r="D17"/>
       <x:c r="E17"/>
@@ -1126,25 +1123,22 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19" s="184" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.7 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
-      <x:c r="C19" s="184"/>
-      <x:c r="D19" s="184"/>
-      <x:c r="E19" s="184"/>
-      <x:c r="F19" s="184"/>
-      <x:c r="G19" s="184"/>
-      <x:c r="H19" s="184"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="184"/>
-      <x:c r="C20" s="184"/>
-      <x:c r="D20" s="184"/>
-      <x:c r="E20" s="184"/>
-      <x:c r="F20" s="184"/>
-      <x:c r="G20" s="184"/>
-      <x:c r="H20" s="184"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="184"/>
@@ -1866,9 +1860,7 @@
       <x:c r="H14" s="165" t="str">
         <x:v>手動再実行はjobId+対象日指定</x:v>
       </x:c>
-      <x:c r="I14" s="165" t="str">
-        <x:v>PGは詳細設計でClass/SQLを定義</x:v>
-      </x:c>
+      <x:c r="I14"/>
       <x:c r="J14" s="165" t="str">
         <x:v>BR-BATCH-001</x:v>
       </x:c>
